--- a/3_annotation_manual/HE/1_manual_curation/fixed_lab_report/fixed_annotation_icl.xlsx
+++ b/3_annotation_manual/HE/1_manual_curation/fixed_lab_report/fixed_annotation_icl.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="718">
   <si>
     <t xml:space="preserve">chrom_peak_id</t>
   </si>
@@ -86,6 +86,9 @@
     <t xml:space="preserve">number_of_peaks</t>
   </si>
   <si>
+    <t xml:space="preserve">polarity</t>
+  </si>
+  <si>
     <t xml:space="preserve">mz_[M-H]-</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
     <t xml:space="preserve">0|0</t>
   </si>
   <si>
+    <t xml:space="preserve">pos</t>
+  </si>
+  <si>
     <t xml:space="preserve">CP444026|CP721301|CP018399</t>
   </si>
   <si>
@@ -137,6 +143,9 @@
     <t xml:space="preserve">0|203.922179624|0</t>
   </si>
   <si>
+    <t xml:space="preserve">neg|pos</t>
+  </si>
+  <si>
     <t xml:space="preserve">CP734871|CP721230|CP017766</t>
   </si>
   <si>
@@ -162,6 +171,9 @@
   </si>
   <si>
     <t xml:space="preserve">493.020422669386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neg</t>
   </si>
   <si>
     <t xml:space="preserve">CP020059</t>
@@ -2561,10 +2573,13 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="n">
         <v>17.6377448818148</v>
@@ -2576,25 +2591,25 @@
         <v>74386.0894672181</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" t="n">
         <v>259.045703038</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" t="n">
         <v>24</v>
@@ -2618,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -2635,12 +2650,15 @@
       <c r="X2" t="n">
         <v>2</v>
       </c>
-      <c r="Y2"/>
+      <c r="Y2" t="s">
+        <v>35</v>
+      </c>
       <c r="Z2"/>
+      <c r="AA2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" t="n">
         <v>21.2947455427148</v>
@@ -2652,25 +2670,25 @@
         <v>51638.2986577465</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I3" t="n">
         <v>342.116211524</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" t="n">
         <v>21</v>
@@ -2694,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -2711,14 +2729,17 @@
       <c r="X3" t="n">
         <v>3</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z3" t="n">
         <v>341.109660418976</v>
       </c>
-      <c r="Z3"/>
+      <c r="AA3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
         <v>17.6377448818148</v>
@@ -2730,25 +2751,25 @@
         <v>706933.942271776</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I4" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
         <v>25</v>
@@ -2772,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -2789,14 +2810,17 @@
       <c r="X4" t="n">
         <v>3</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" t="n">
         <v>225.099192339699</v>
       </c>
-      <c r="Z4"/>
+      <c r="AA4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B5" t="n">
         <v>95.8249799180902</v>
@@ -2808,25 +2832,25 @@
         <v>405.132739768991</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I5" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2850,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
@@ -2863,14 +2887,17 @@
       <c r="X5" t="n">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5" t="n">
+      <c r="Y5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z5"/>
+      <c r="AA5" t="n">
         <v>271.067237812475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B6" t="n">
         <v>175.636122074771</v>
@@ -2882,25 +2909,25 @@
         <v>4031.23184349504</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I6" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
         <v>7</v>
@@ -2924,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="T6" t="n">
         <v>3</v>
@@ -2939,12 +2966,15 @@
       <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="Y6"/>
+      <c r="Y6" t="s">
+        <v>35</v>
+      </c>
       <c r="Z6"/>
+      <c r="AA6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B7" t="n">
         <v>214.381974971778</v>
@@ -2956,25 +2986,25 @@
         <v>5800.33999893627</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I7" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
@@ -2998,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="T7" t="n">
         <v>4</v>
@@ -3013,12 +3043,15 @@
       <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7"/>
+      <c r="Y7" t="s">
+        <v>35</v>
+      </c>
       <c r="Z7"/>
+      <c r="AA7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B8" t="n">
         <v>256.709696282462</v>
@@ -3030,25 +3063,25 @@
         <v>7194.17531307019</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I8" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -3072,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T8" t="n">
         <v>5</v>
@@ -3085,14 +3118,17 @@
       <c r="X8" t="n">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8" t="n">
+      <c r="Y8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z8"/>
+      <c r="AA8" t="n">
         <v>271.096881597408</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B9" t="n">
         <v>298.055728944623</v>
@@ -3104,25 +3140,25 @@
         <v>8526.2784649535</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
@@ -3146,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="T9" t="n">
         <v>6</v>
@@ -3161,12 +3197,15 @@
       <c r="X9" t="n">
         <v>1</v>
       </c>
-      <c r="Y9"/>
+      <c r="Y9" t="s">
+        <v>35</v>
+      </c>
       <c r="Z9"/>
+      <c r="AA9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B10" t="n">
         <v>336.777112867661</v>
@@ -3178,25 +3217,25 @@
         <v>1432.1353712474</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I10" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
@@ -3220,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="T10" t="n">
         <v>7</v>
@@ -3233,16 +3272,19 @@
       <c r="X10" t="n">
         <v>2</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y10" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z10" t="n">
         <v>225.136349900313</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>271.134896928893</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B11" t="n">
         <v>357.11429621767</v>
@@ -3254,25 +3296,25 @@
         <v>6021.86838057574</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I11" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>3</v>
@@ -3296,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="T11" t="n">
         <v>8</v>
@@ -3309,14 +3351,17 @@
       <c r="X11" t="n">
         <v>1</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y11" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z11" t="n">
         <v>225.052360672899</v>
       </c>
-      <c r="Z11"/>
+      <c r="AA11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B12" t="n">
         <v>377.948239072971</v>
@@ -3328,25 +3373,25 @@
         <v>1156.30733146542</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I12" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -3370,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="T12" t="n">
         <v>9</v>
@@ -3383,14 +3428,17 @@
       <c r="X12" t="n">
         <v>1</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y12" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z12" t="n">
         <v>225.079685658215</v>
       </c>
-      <c r="Z12"/>
+      <c r="AA12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B13" t="n">
         <v>513.847664013239</v>
@@ -3402,25 +3450,25 @@
         <v>5197.54097415523</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I13" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
@@ -3444,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="T13" t="n">
         <v>10</v>
@@ -3459,12 +3507,15 @@
       <c r="X13" t="n">
         <v>1</v>
       </c>
-      <c r="Y13"/>
+      <c r="Y13" t="s">
+        <v>35</v>
+      </c>
       <c r="Z13"/>
+      <c r="AA13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B14" t="n">
         <v>566.488950404847</v>
@@ -3476,25 +3527,25 @@
         <v>4653.40275543507</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I14" t="n">
         <v>226.106590308</v>
       </c>
       <c r="J14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
         <v>6</v>
@@ -3518,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T14" t="n">
         <v>11</v>
@@ -3535,12 +3586,15 @@
       <c r="X14" t="n">
         <v>2</v>
       </c>
-      <c r="Y14"/>
+      <c r="Y14" t="s">
+        <v>35</v>
+      </c>
       <c r="Z14"/>
+      <c r="AA14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B15" t="n">
         <v>21.2947455427148</v>
@@ -3552,25 +3606,25 @@
         <v>1114148.52798389</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I15" t="n">
         <v>307.083806264</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L15" t="n">
         <v>34</v>
@@ -3594,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -3611,14 +3665,17 @@
       <c r="X15" t="n">
         <v>3</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z15" t="n">
         <v>306.078140429725</v>
       </c>
-      <c r="Z15"/>
+      <c r="AA15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B16" t="n">
         <v>21.2947455427148</v>
@@ -3630,25 +3687,25 @@
         <v>492567.533510675</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I16" t="n">
         <v>363.057999038</v>
       </c>
       <c r="J16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L16" t="n">
         <v>24</v>
@@ -3672,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -3689,14 +3746,17 @@
       <c r="X16" t="n">
         <v>3</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y16" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z16" t="n">
         <v>362.051655616644</v>
       </c>
-      <c r="Z16"/>
+      <c r="AA16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B17" t="n">
         <v>19.5228113213327</v>
@@ -3708,25 +3768,25 @@
         <v>70749.0187530555</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I17" t="n">
         <v>268.055148992</v>
       </c>
       <c r="J17" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L17" t="n">
         <v>11</v>
@@ -3750,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -3765,14 +3825,17 @@
       <c r="X17" t="n">
         <v>2</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z17" t="n">
         <v>267.04895674019</v>
       </c>
-      <c r="Z17"/>
+      <c r="AA17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B18" t="n">
         <v>19.6947452804348</v>
@@ -3784,25 +3847,25 @@
         <v>24292.2632926016</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F18" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I18" t="n">
         <v>119.058243147999</v>
       </c>
       <c r="J18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L18" t="n">
         <v>16</v>
@@ -3826,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
@@ -3841,16 +3904,19 @@
       <c r="X18" t="n">
         <v>3</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z18" t="n">
         <v>118.051337205089</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>164.0917059893</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B19" t="n">
         <v>39.6691302497477</v>
@@ -3862,25 +3928,25 @@
         <v>11232.1460779507</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H19" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I19" t="n">
         <v>119.058243147999</v>
       </c>
       <c r="J19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -3904,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T19" t="n">
         <v>2</v>
@@ -3917,14 +3983,17 @@
       <c r="X19" t="n">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19" t="n">
+      <c r="Y19" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z19"/>
+      <c r="AA19" t="n">
         <v>164.021399412525</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B20" t="n">
         <v>63.7605874506169</v>
@@ -3936,25 +4005,25 @@
         <v>3039.75718648151</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G20" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I20" t="n">
         <v>119.058243147999</v>
       </c>
       <c r="J20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L20" t="n">
         <v>5</v>
@@ -3978,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="T20" t="n">
         <v>3</v>
@@ -3991,16 +4060,19 @@
       <c r="X20" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y20" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z20" t="n">
         <v>118.018045921982</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>164.021159495234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B21" t="n">
         <v>240.632007571399</v>
@@ -4012,25 +4084,25 @@
         <v>2248.29711518764</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G21" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I21" t="n">
         <v>119.058243147999</v>
       </c>
       <c r="J21" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L21" t="n">
         <v>5</v>
@@ -4054,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="T21" t="n">
         <v>4</v>
@@ -4069,12 +4141,15 @@
       <c r="X21" t="n">
         <v>1</v>
       </c>
-      <c r="Y21"/>
+      <c r="Y21" t="s">
+        <v>35</v>
+      </c>
       <c r="Z21"/>
+      <c r="AA21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B22" t="n">
         <v>279.276101623312</v>
@@ -4086,25 +4161,25 @@
         <v>4048.74148304726</v>
       </c>
       <c r="E22" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I22" t="n">
         <v>119.058243147999</v>
       </c>
       <c r="J22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L22" t="n">
         <v>8</v>
@@ -4128,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="T22" t="n">
         <v>5</v>
@@ -4145,12 +4220,15 @@
       <c r="X22" t="n">
         <v>2</v>
       </c>
-      <c r="Y22"/>
+      <c r="Y22" t="s">
+        <v>35</v>
+      </c>
       <c r="Z22"/>
+      <c r="AA22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B23" t="n">
         <v>17.8667447349548</v>
@@ -4162,25 +4240,25 @@
         <v>50162.2488503643</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H23" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I23" t="n">
         <v>146.105527688</v>
       </c>
       <c r="J23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L23" t="n">
         <v>32</v>
@@ -4204,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
@@ -4221,14 +4299,17 @@
       <c r="X23" t="n">
         <v>3</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y23" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z23" t="n">
         <v>145.097130850085</v>
       </c>
-      <c r="Z23"/>
+      <c r="AA23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B24" t="n">
         <v>21.2947455427148</v>
@@ -4240,25 +4321,25 @@
         <v>1393031.1971742</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G24" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H24" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I24" t="n">
         <v>188.116092372</v>
       </c>
       <c r="J24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L24" t="n">
         <v>14</v>
@@ -4282,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
@@ -4297,14 +4378,17 @@
       <c r="X24" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Y24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z24" t="n">
         <v>187.109830175377</v>
       </c>
-      <c r="Z24"/>
+      <c r="AA24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B25" t="n">
         <v>19.0087452909548</v>
@@ -4316,25 +4400,25 @@
         <v>199037.811452167</v>
       </c>
       <c r="E25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H25" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I25" t="n">
         <v>261.040223734</v>
       </c>
       <c r="J25" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L25" t="n">
         <v>29</v>
@@ -4358,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
@@ -4375,14 +4459,17 @@
       <c r="X25" t="n">
         <v>3</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Y25" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z25" t="n">
         <v>260.034309180847</v>
       </c>
-      <c r="Z25"/>
+      <c r="AA25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B26" t="n">
         <v>22.037811823606</v>
@@ -4394,25 +4481,25 @@
         <v>1028.30455876099</v>
       </c>
       <c r="E26" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H26" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I26" t="n">
         <v>399.145063836</v>
       </c>
       <c r="J26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -4436,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
@@ -4449,14 +4536,17 @@
       <c r="X26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26" t="n">
+      <c r="Y26" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z26"/>
+      <c r="AA26" t="n">
         <v>444.125707913023</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B27" t="n">
         <v>18.7807450076948</v>
@@ -4468,25 +4558,25 @@
         <v>55662.1416835971</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F27" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G27" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H27" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I27" t="n">
         <v>89.047678464</v>
       </c>
       <c r="J27" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L27" t="n">
         <v>10</v>
@@ -4510,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
@@ -4525,14 +4615,17 @@
       <c r="X27" t="n">
         <v>2</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Y27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z27" t="n">
         <v>88.0401824985744</v>
       </c>
-      <c r="Z27"/>
+      <c r="AA27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B28" t="n">
         <v>21.5237453958548</v>
@@ -4544,25 +4637,25 @@
         <v>1066756.69544846</v>
       </c>
       <c r="E28" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H28" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I28" t="n">
         <v>324.035866626</v>
       </c>
       <c r="J28" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L28" t="n">
         <v>18</v>
@@ -4586,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
@@ -4601,14 +4694,17 @@
       <c r="X28" t="n">
         <v>2</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Y28" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z28" t="n">
         <v>323.030889293839</v>
       </c>
-      <c r="Z28"/>
+      <c r="AA28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B29" t="n">
         <v>22.2087458154548</v>
@@ -4620,25 +4716,25 @@
         <v>2852220.90916535</v>
       </c>
       <c r="E29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H29" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I29" t="n">
         <v>268.117154992</v>
       </c>
       <c r="J29" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L29" t="n">
         <v>33</v>
@@ -4662,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
@@ -4679,14 +4775,17 @@
       <c r="X29" t="n">
         <v>3</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y29" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z29" t="n">
         <v>267.110095651325</v>
       </c>
-      <c r="Z29"/>
+      <c r="AA29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B30" t="n">
         <v>20.6087455531748</v>
@@ -4698,25 +4797,25 @@
         <v>52833.4898545723</v>
       </c>
       <c r="E30" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F30" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G30" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H30" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I30" t="n">
         <v>489.115155944</v>
       </c>
       <c r="J30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K30" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L30" t="n">
         <v>20</v>
@@ -4740,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
@@ -4757,12 +4856,15 @@
       <c r="X30" t="n">
         <v>2</v>
       </c>
-      <c r="Y30"/>
+      <c r="Y30" t="s">
+        <v>35</v>
+      </c>
       <c r="Z30"/>
+      <c r="AA30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B31" t="n">
         <v>20.6087455531748</v>
@@ -4774,25 +4876,25 @@
         <v>300067.313118562</v>
       </c>
       <c r="E31" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F31" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G31" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H31" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I31" t="n">
         <v>323.051851038</v>
       </c>
       <c r="J31" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K31" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L31" t="n">
         <v>28</v>
@@ -4816,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
@@ -4833,14 +4935,17 @@
       <c r="X31" t="n">
         <v>3</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Y31" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z31" t="n">
         <v>322.043778456301</v>
       </c>
-      <c r="Z31"/>
+      <c r="AA31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B32" t="n">
         <v>155.758584745153</v>
@@ -4852,25 +4957,25 @@
         <v>537784.31570608</v>
       </c>
       <c r="E32" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F32" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G32" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H32" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I32" t="n">
         <v>441.139681328</v>
       </c>
       <c r="J32" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K32" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L32" t="n">
         <v>19</v>
@@ -4894,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="T32" t="n">
         <v>5</v>
@@ -4911,14 +5016,17 @@
       <c r="X32" t="n">
         <v>3</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Y32" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z32" t="n">
         <v>440.134581138006</v>
       </c>
-      <c r="Z32"/>
+      <c r="AA32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B33" t="n">
         <v>21.5237453958548</v>
@@ -4930,25 +5038,25 @@
         <v>970937.398878571</v>
       </c>
       <c r="E33" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F33" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G33" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H33" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I33" t="n">
         <v>348.047100006</v>
       </c>
       <c r="J33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K33" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L33" t="n">
         <v>45</v>
@@ -4972,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
@@ -4989,14 +5097,17 @@
       <c r="X33" t="n">
         <v>3</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Y33" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z33" t="n">
         <v>347.039326315033</v>
       </c>
-      <c r="Z33"/>
+      <c r="AA33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B34" t="n">
         <v>40.447182776739</v>
@@ -5008,25 +5119,25 @@
         <v>135710.213319989</v>
       </c>
       <c r="E34" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G34" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H34" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I34" t="n">
         <v>208.084792244</v>
       </c>
       <c r="J34" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L34" t="n">
         <v>8</v>
@@ -5050,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="T34" t="n">
         <v>2</v>
@@ -5065,14 +5176,17 @@
       <c r="X34" t="n">
         <v>2</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Y34" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z34" t="n">
         <v>207.076830477747</v>
       </c>
-      <c r="Z34"/>
+      <c r="AA34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B35" t="n">
         <v>20.6087455531748</v>
@@ -5084,25 +5198,25 @@
         <v>182359.117911552</v>
       </c>
       <c r="E35" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F35" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G35" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H35" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I35" t="n">
         <v>189.11134134</v>
       </c>
       <c r="J35" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K35" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L35" t="n">
         <v>31</v>
@@ -5126,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
@@ -5143,16 +5257,19 @@
       <c r="X35" t="n">
         <v>4</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Y35" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z35" t="n">
         <v>188.103634806268</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>234.136817259222</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B36" t="n">
         <v>88.2501388506573</v>
@@ -5164,25 +5281,25 @@
         <v>641053.759665899</v>
       </c>
       <c r="E36" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F36" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G36" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H36" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I36" t="n">
         <v>204.089877624</v>
       </c>
       <c r="J36" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K36" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L36" t="n">
         <v>25</v>
@@ -5206,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="T36" t="n">
         <v>4</v>
@@ -5223,14 +5340,17 @@
       <c r="X36" t="n">
         <v>3</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Y36" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z36" t="n">
         <v>203.082548556202</v>
       </c>
-      <c r="Z36"/>
+      <c r="AA36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B37" t="n">
         <v>22.4867085141901</v>
@@ -5242,25 +5362,25 @@
         <v>386280.966480924</v>
       </c>
       <c r="E37" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F37" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G37" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H37" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I37" t="n">
         <v>188.079706864</v>
       </c>
       <c r="J37" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K37" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L37" t="n">
         <v>16</v>
@@ -5284,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
@@ -5299,14 +5419,17 @@
       <c r="X37" t="n">
         <v>2</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Y37" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z37" t="n">
         <v>187.072529552193</v>
       </c>
-      <c r="Z37"/>
+      <c r="AA37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B38" t="n">
         <v>24.2647448560748</v>
@@ -5318,25 +5441,25 @@
         <v>117183.000404244</v>
       </c>
       <c r="E38" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G38" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H38" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I38" t="n">
         <v>190.05897142</v>
       </c>
       <c r="J38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K38" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L38" t="n">
         <v>11</v>
@@ -5360,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
@@ -5375,14 +5498,17 @@
       <c r="X38" t="n">
         <v>2</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Y38" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z38" t="n">
         <v>189.052269692443</v>
       </c>
-      <c r="Z38"/>
+      <c r="AA38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B39" t="n">
         <v>39.1946636907121</v>
@@ -5394,25 +5520,25 @@
         <v>915048.567416683</v>
       </c>
       <c r="E39" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F39" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G39" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="H39" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I39" t="n">
         <v>285.0960852</v>
       </c>
       <c r="J39" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K39" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L39" t="n">
         <v>13</v>
@@ -5436,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -5451,14 +5577,17 @@
       <c r="X39" t="n">
         <v>2</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Y39" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z39" t="n">
         <v>284.088132523137</v>
       </c>
-      <c r="Z39"/>
+      <c r="AA39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B40" t="n">
         <v>19.6947452804348</v>
@@ -5470,25 +5599,25 @@
         <v>122119.708928329</v>
       </c>
       <c r="E40" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F40" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G40" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H40" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I40" t="n">
         <v>663.109121804</v>
       </c>
       <c r="J40" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K40" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L40" t="n">
         <v>18</v>
@@ -5512,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
@@ -5529,14 +5658,17 @@
       <c r="X40" t="n">
         <v>3</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Y40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z40" t="n">
         <v>662.096023984409</v>
       </c>
-      <c r="Z40"/>
+      <c r="AA40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B41" t="n">
         <v>24.0367445728148</v>
@@ -5548,25 +5680,25 @@
         <v>303674.93215811</v>
       </c>
       <c r="E41" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F41" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G41" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H41" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I41" t="n">
         <v>665.124771867999</v>
       </c>
       <c r="J41" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K41" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L41" t="n">
         <v>20</v>
@@ -5590,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
@@ -5607,14 +5739,17 @@
       <c r="X41" t="n">
         <v>3</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Y41" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z41" t="n">
         <v>664.114656930746</v>
       </c>
-      <c r="Z41"/>
+      <c r="AA41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B42" t="n">
         <v>21.2947455427148</v>
@@ -5626,25 +5761,25 @@
         <v>5816.86409478248</v>
       </c>
       <c r="E42" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F42" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G42" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H42" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I42" t="n">
         <v>89.047678464</v>
       </c>
       <c r="J42" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L42" t="n">
         <v>9</v>
@@ -5668,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
@@ -5683,14 +5818,17 @@
       <c r="X42" t="n">
         <v>2</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Y42" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z42" t="n">
         <v>88.0110697155551</v>
       </c>
-      <c r="Z42"/>
+      <c r="AA42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B43" t="n">
         <v>24.3059392340275</v>
@@ -5702,25 +5840,25 @@
         <v>1607968.90421136</v>
       </c>
       <c r="E43" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F43" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G43" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H43" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I43" t="n">
         <v>192.027002596</v>
       </c>
       <c r="J43" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K43" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L43" t="n">
         <v>5</v>
@@ -5744,7 +5882,7 @@
         <v>1</v>
       </c>
       <c r="S43" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
@@ -5757,14 +5895,17 @@
       <c r="X43" t="n">
         <v>1</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Y43" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z43" t="n">
         <v>191.02042547026</v>
       </c>
-      <c r="Z43"/>
+      <c r="AA43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B44" t="n">
         <v>24.0367445728148</v>
@@ -5776,25 +5917,25 @@
         <v>143634.953460869</v>
       </c>
       <c r="E44" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F44" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G44" t="s">
+        <v>228</v>
+      </c>
+      <c r="H44" t="s">
         <v>224</v>
-      </c>
-      <c r="H44" t="s">
-        <v>220</v>
       </c>
       <c r="I44" t="n">
         <v>192.027002596</v>
       </c>
       <c r="J44" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K44" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L44" t="n">
         <v>8</v>
@@ -5818,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
@@ -5833,12 +5974,15 @@
       <c r="X44" t="n">
         <v>1</v>
       </c>
-      <c r="Y44"/>
+      <c r="Y44" t="s">
+        <v>35</v>
+      </c>
       <c r="Z44"/>
+      <c r="AA44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B45" t="n">
         <v>18.7807450076948</v>
@@ -5850,25 +5994,25 @@
         <v>283945.838475437</v>
       </c>
       <c r="E45" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F45" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G45" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H45" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I45" t="n">
         <v>131.069476528</v>
       </c>
       <c r="J45" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K45" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L45" t="n">
         <v>13</v>
@@ -5892,7 +6036,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
@@ -5909,14 +6053,17 @@
       <c r="X45" t="n">
         <v>3</v>
       </c>
-      <c r="Y45"/>
-      <c r="Z45" t="n">
+      <c r="Y45" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z45"/>
+      <c r="AA45" t="n">
         <v>176.098426972895</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B46" t="n">
         <v>22.4377456685948</v>
@@ -5928,25 +6075,25 @@
         <v>419034.688304617</v>
       </c>
       <c r="E46" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F46" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G46" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H46" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I46" t="n">
         <v>612.151962464</v>
       </c>
       <c r="J46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K46" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L46" t="n">
         <v>15</v>
@@ -5970,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
@@ -5987,12 +6134,15 @@
       <c r="X46" t="n">
         <v>2</v>
       </c>
-      <c r="Y46"/>
+      <c r="Y46" t="s">
+        <v>35</v>
+      </c>
       <c r="Z46"/>
+      <c r="AA46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B47" t="n">
         <v>18.7807450076948</v>
@@ -6004,25 +6154,25 @@
         <v>815485.895183295</v>
       </c>
       <c r="E47" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F47" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G47" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H47" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I47" t="n">
         <v>188.127325752</v>
       </c>
       <c r="J47" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K47" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L47" t="n">
         <v>23</v>
@@ -6046,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
@@ -6063,16 +6213,19 @@
       <c r="X47" t="n">
         <v>4</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Y47" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z47" t="n">
         <v>187.111771332123</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>233.098815104783</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B48" t="n">
         <v>146.861459508749</v>
@@ -6084,25 +6237,25 @@
         <v>604015.014327354</v>
       </c>
       <c r="E48" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F48" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G48" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H48" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I48" t="n">
         <v>179.058243148</v>
       </c>
       <c r="J48" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K48" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L48" t="n">
         <v>16</v>
@@ -6126,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="S48" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="T48" t="n">
         <v>2</v>
@@ -6143,14 +6296,17 @@
       <c r="X48" t="n">
         <v>3</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Y48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z48" t="n">
         <v>178.051142207454</v>
       </c>
-      <c r="Z48"/>
+      <c r="AA48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B49" t="n">
         <v>154.617816126326</v>
@@ -6162,25 +6318,25 @@
         <v>4038839.67844632</v>
       </c>
       <c r="E49" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F49" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G49" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H49" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I49" t="n">
         <v>264.111006992</v>
       </c>
       <c r="J49" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K49" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L49" t="n">
         <v>34</v>
@@ -6204,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
@@ -6221,14 +6377,17 @@
       <c r="X49" t="n">
         <v>3</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y49" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z49" t="n">
         <v>263.1039479195</v>
       </c>
-      <c r="Z49"/>
+      <c r="AA49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B50" t="n">
         <v>18.3237448713548</v>
@@ -6240,25 +6399,25 @@
         <v>49953.5965489863</v>
       </c>
       <c r="E50" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F50" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G50" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H50" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I50" t="n">
         <v>141.019094366</v>
       </c>
       <c r="J50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K50" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L50" t="n">
         <v>17</v>
@@ -6282,7 +6441,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
@@ -6299,12 +6458,15 @@
       <c r="X50" t="n">
         <v>2</v>
       </c>
-      <c r="Y50"/>
+      <c r="Y50" t="s">
+        <v>35</v>
+      </c>
       <c r="Z50"/>
+      <c r="AA50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B51" t="n">
         <v>18.5901471985826</v>
@@ -6316,25 +6478,25 @@
         <v>484050.142199915</v>
       </c>
       <c r="E51" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F51" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G51" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H51" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I51" t="n">
         <v>260.029718626</v>
       </c>
       <c r="J51" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K51" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L51" t="n">
         <v>9</v>
@@ -6358,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
@@ -6373,14 +6535,17 @@
       <c r="X51" t="n">
         <v>2</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Y51" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z51" t="n">
         <v>259.022267925568</v>
       </c>
-      <c r="Z51"/>
+      <c r="AA51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B52" t="n">
         <v>21.104036670276</v>
@@ -6392,25 +6557,25 @@
         <v>375534.543064251</v>
       </c>
       <c r="E52" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F52" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G52" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H52" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I52" t="n">
         <v>243.085520516</v>
       </c>
       <c r="J52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K52" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L52" t="n">
         <v>18</v>
@@ -6434,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
@@ -6451,12 +6616,15 @@
       <c r="X52" t="n">
         <v>2</v>
       </c>
-      <c r="Y52"/>
+      <c r="Y52" t="s">
+        <v>35</v>
+      </c>
       <c r="Z52"/>
+      <c r="AA52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B53" t="n">
         <v>17.6761471245226</v>
@@ -6468,25 +6636,25 @@
         <v>821327.458971777</v>
       </c>
       <c r="E53" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F53" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G53" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H53" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I53" t="n">
         <v>174.111675688</v>
       </c>
       <c r="J53" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K53" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L53" t="n">
         <v>29</v>
@@ -6510,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="S53" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
@@ -6527,14 +6695,17 @@
       <c r="X53" t="n">
         <v>3</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Y53" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z53" t="n">
         <v>173.104896226804</v>
       </c>
-      <c r="Z53"/>
+      <c r="AA53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B54" t="n">
         <v>18.5901471985826</v>
@@ -6546,25 +6717,25 @@
         <v>24072.4841012618</v>
       </c>
       <c r="E54" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F54" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G54" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H54" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I54" t="n">
         <v>240.023848864</v>
       </c>
       <c r="J54" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K54" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L54" t="n">
         <v>29</v>
@@ -6588,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
@@ -6605,16 +6776,19 @@
       <c r="X54" t="n">
         <v>4</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Y54" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z54" t="n">
         <v>239.015789002355</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
         <v>285.020199387716</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B55" t="n">
         <v>19.276036124796</v>
@@ -6626,25 +6800,25 @@
         <v>44560.1444491461</v>
       </c>
       <c r="E55" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F55" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G55" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H55" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="I55" t="n">
         <v>146.06914218</v>
       </c>
       <c r="J55" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K55" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L55" t="n">
         <v>15</v>
@@ -6668,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="S55" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
@@ -6685,14 +6859,17 @@
       <c r="X55" t="n">
         <v>3</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Y55" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z55" t="n">
         <v>145.062221635033</v>
       </c>
-      <c r="Z55"/>
+      <c r="AA55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B56" t="n">
         <v>19.1263230013028</v>
@@ -6704,25 +6881,25 @@
         <v>155017.591125032</v>
       </c>
       <c r="E56" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F56" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G56" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H56" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I56" t="n">
         <v>215.03492086</v>
       </c>
       <c r="J56" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K56" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L56" t="n">
         <v>20</v>
@@ -6746,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
@@ -6763,16 +6940,19 @@
       <c r="X56" t="n">
         <v>4</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Y56" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z56" t="n">
         <v>214.01938534754</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AA56" t="n">
         <v>260.042868508007</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B57" t="n">
         <v>17.7145493672304</v>
@@ -6784,25 +6964,25 @@
         <v>59790.7783870095</v>
       </c>
       <c r="E57" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F57" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G57" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H57" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I57" t="n">
         <v>121.019749464</v>
       </c>
       <c r="J57" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K57" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L57" t="n">
         <v>17</v>
@@ -6826,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T57" t="n">
         <v>1</v>
@@ -6843,14 +7023,17 @@
       <c r="X57" t="n">
         <v>3</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Y57" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z57" t="n">
         <v>120.013090546922</v>
       </c>
-      <c r="Z57"/>
+      <c r="AA57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B58" t="n">
         <v>18.1715491062571</v>
@@ -6862,25 +7045,25 @@
         <v>738008.192397966</v>
       </c>
       <c r="E58" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F58" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G58" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H58" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I58" t="n">
         <v>155.069476528</v>
       </c>
       <c r="J58" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K58" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L58" t="n">
         <v>25</v>
@@ -6904,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
@@ -6921,16 +7104,19 @@
       <c r="X58" t="n">
         <v>4</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Y58" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z58" t="n">
         <v>154.062681456665</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AA58" t="n">
         <v>200.081093436648</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B59" t="n">
         <v>21.1423276509771</v>
@@ -6942,25 +7128,25 @@
         <v>65372.8948499423</v>
       </c>
       <c r="E59" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F59" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G59" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="H59" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I59" t="n">
         <v>165.045964212</v>
       </c>
       <c r="J59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K59" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L59" t="n">
         <v>18</v>
@@ -6984,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
@@ -7001,12 +7187,15 @@
       <c r="X59" t="n">
         <v>2</v>
       </c>
-      <c r="Y59"/>
+      <c r="Y59" t="s">
+        <v>35</v>
+      </c>
       <c r="Z59"/>
+      <c r="AA59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B60" t="n">
         <v>19.5835452642961</v>
@@ -7018,25 +7207,25 @@
         <v>18255.9456982306</v>
       </c>
       <c r="E60" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F60" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G60" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H60" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I60" t="n">
         <v>119.058243147999</v>
       </c>
       <c r="J60" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K60" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L60" t="n">
         <v>13</v>
@@ -7060,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
@@ -7077,14 +7266,17 @@
       <c r="X60" t="n">
         <v>3</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Y60" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z60" t="n">
         <v>118.050489285119</v>
       </c>
-      <c r="Z60"/>
+      <c r="AA60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B61" t="n">
         <v>20.4565497881371</v>
@@ -7096,25 +7288,25 @@
         <v>5475013.143451</v>
       </c>
       <c r="E61" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F61" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G61" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H61" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I61" t="n">
         <v>216.122240372</v>
       </c>
       <c r="J61" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K61" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L61" t="n">
         <v>27</v>
@@ -7138,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
@@ -7155,16 +7347,19 @@
       <c r="X61" t="n">
         <v>4</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="Y61" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z61" t="n">
         <v>215.11629431086</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AA61" t="n">
         <v>261.083624250479</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B62" t="n">
         <v>22.7419928843682</v>
@@ -7176,25 +7371,25 @@
         <v>376397.685619166</v>
       </c>
       <c r="E62" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F62" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G62" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H62" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I62" t="n">
         <v>267.096753896</v>
       </c>
       <c r="J62" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K62" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L62" t="n">
         <v>26</v>
@@ -7218,7 +7413,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
@@ -7235,14 +7430,17 @@
       <c r="X62" t="n">
         <v>3</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="Y62" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z62" t="n">
         <v>266.088181300428</v>
       </c>
-      <c r="Z62"/>
+      <c r="AA62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B63" t="n">
         <v>20.0379516957582</v>
@@ -7254,25 +7452,25 @@
         <v>176483.862536306</v>
       </c>
       <c r="E63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F63" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G63" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H63" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I63" t="n">
         <v>241.10625596</v>
       </c>
       <c r="J63" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K63" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L63" t="n">
         <v>20</v>
@@ -7296,7 +7494,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -7313,14 +7511,17 @@
       <c r="X63" t="n">
         <v>3</v>
       </c>
-      <c r="Y63" t="n">
+      <c r="Y63" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z63" t="n">
         <v>240.095997245597</v>
       </c>
-      <c r="Z63"/>
+      <c r="AA63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B64" t="n">
         <v>41.4699982460871</v>
@@ -7332,25 +7533,25 @@
         <v>403811.222966277</v>
       </c>
       <c r="E64" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F64" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G64" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="H64" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="I64" t="n">
         <v>165.078978592</v>
       </c>
       <c r="J64" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K64" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L64" t="n">
         <v>22</v>
@@ -7374,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="T64" t="n">
         <v>2</v>
@@ -7391,14 +7592,17 @@
       <c r="X64" t="n">
         <v>3</v>
       </c>
-      <c r="Y64" t="n">
+      <c r="Y64" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z64" t="n">
         <v>164.070876572015</v>
       </c>
-      <c r="Z64"/>
+      <c r="AA64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B65" t="n">
         <v>19.5809515593782</v>
@@ -7410,25 +7614,25 @@
         <v>185643.482525741</v>
       </c>
       <c r="E65" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F65" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G65" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H65" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="I65" t="n">
         <v>168.089877624</v>
       </c>
       <c r="J65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K65" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L65" t="n">
         <v>23</v>
@@ -7452,7 +7656,7 @@
         <v>0</v>
       </c>
       <c r="S65" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
@@ -7469,12 +7673,15 @@
       <c r="X65" t="n">
         <v>2</v>
       </c>
-      <c r="Y65"/>
+      <c r="Y65" t="s">
+        <v>35</v>
+      </c>
       <c r="Z65"/>
+      <c r="AA65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B66" t="n">
         <v>79.8712381943271</v>
@@ -7486,25 +7693,25 @@
         <v>2456664.10700945</v>
       </c>
       <c r="E66" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F66" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G66" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H66" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I66" t="n">
         <v>306.97054118</v>
       </c>
       <c r="J66" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L66" t="n">
         <v>14</v>
@@ -7528,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="T66" t="n">
         <v>3</v>
@@ -7543,14 +7750,17 @@
       <c r="X66" t="n">
         <v>2</v>
       </c>
-      <c r="Y66" t="n">
+      <c r="Y66" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z66" t="n">
         <v>305.963535735658</v>
       </c>
-      <c r="Z66"/>
+      <c r="AA66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B67" t="n">
         <v>276.970898573879</v>
@@ -7562,25 +7772,25 @@
         <v>4138310.44655478</v>
       </c>
       <c r="E67" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F67" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G67" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H67" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="I67" t="n">
         <v>650.790051864</v>
       </c>
       <c r="J67" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K67" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L67" t="n">
         <v>25</v>
@@ -7604,7 +7814,7 @@
         <v>0</v>
       </c>
       <c r="S67" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
@@ -7619,16 +7829,19 @@
       <c r="X67" t="n">
         <v>3</v>
       </c>
-      <c r="Y67" t="n">
+      <c r="Y67" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z67" t="n">
         <v>649.785123837946</v>
       </c>
-      <c r="Z67" t="n">
+      <c r="AA67" t="n">
         <v>695.789620562867</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B68" t="n">
         <v>204.601223745863</v>
@@ -7640,25 +7853,25 @@
         <v>2325393.50913039</v>
       </c>
       <c r="E68" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F68" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G68" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H68" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="I68" t="n">
         <v>168.042258736</v>
       </c>
       <c r="J68" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L68" t="n">
         <v>10</v>
@@ -7682,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="T68" t="n">
         <v>6</v>
@@ -7697,14 +7910,17 @@
       <c r="X68" t="n">
         <v>2</v>
       </c>
-      <c r="Y68" t="n">
+      <c r="Y68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z68" t="n">
         <v>167.035601471236</v>
       </c>
-      <c r="Z68"/>
+      <c r="AA68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B69" t="n">
         <v>168.724381946855</v>
@@ -7716,25 +7932,25 @@
         <v>4386179.15964179</v>
       </c>
       <c r="E69" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F69" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G69" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H69" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="I69" t="n">
         <v>244.088163372</v>
       </c>
       <c r="J69" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K69" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L69" t="n">
         <v>31</v>
@@ -7758,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="T69" t="n">
         <v>3</v>
@@ -7775,14 +7991,17 @@
       <c r="X69" t="n">
         <v>3</v>
       </c>
-      <c r="Y69" t="n">
+      <c r="Y69" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z69" t="n">
         <v>243.081893216159</v>
       </c>
-      <c r="Z69"/>
+      <c r="AA69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B70" t="n">
         <v>299.620686679183</v>
@@ -7794,25 +8013,25 @@
         <v>3513110.11425235</v>
       </c>
       <c r="E70" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F70" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G70" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H70" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I70" t="n">
         <v>346.21440944</v>
       </c>
       <c r="J70" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K70" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L70" t="n">
         <v>37</v>
@@ -7836,7 +8055,7 @@
         <v>1</v>
       </c>
       <c r="S70" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="T70" t="n">
         <v>8</v>
@@ -7853,16 +8072,19 @@
       <c r="X70" t="n">
         <v>4</v>
       </c>
-      <c r="Y70" t="n">
+      <c r="Y70" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z70" t="n">
         <v>345.203729943545</v>
       </c>
-      <c r="Z70" t="n">
+      <c r="AA70" t="n">
         <v>391.213338268079</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B71" t="n">
         <v>120.810842939475</v>
@@ -7874,25 +8096,25 @@
         <v>6791761.23856544</v>
       </c>
       <c r="E71" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F71" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G71" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H71" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="I71" t="n">
         <v>189.042593084</v>
       </c>
       <c r="J71" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K71" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L71" t="n">
         <v>11</v>
@@ -7916,7 +8138,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="T71" t="n">
         <v>5</v>
@@ -7931,14 +8153,17 @@
       <c r="X71" t="n">
         <v>2</v>
       </c>
-      <c r="Y71" t="n">
+      <c r="Y71" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z71" t="n">
         <v>188.035648879145</v>
       </c>
-      <c r="Z71"/>
+      <c r="AA71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B72" t="n">
         <v>22.7945863042101</v>
@@ -7950,25 +8175,25 @@
         <v>59238.7012878908</v>
       </c>
       <c r="E72" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F72" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="G72" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H72" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I72" t="n">
         <v>149.051049592</v>
       </c>
       <c r="J72" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K72" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L72" t="n">
         <v>9</v>
@@ -7992,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="S72" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="T72" t="n">
         <v>1</v>
@@ -8007,14 +8232,17 @@
       <c r="X72" t="n">
         <v>2</v>
       </c>
-      <c r="Y72" t="n">
+      <c r="Y72" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z72" t="n">
         <v>148.044608720017</v>
       </c>
-      <c r="Z72"/>
+      <c r="AA72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B73" t="n">
         <v>43.9928415247057</v>
@@ -8026,25 +8254,25 @@
         <v>1096520.17869168</v>
       </c>
       <c r="E73" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F73" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G73" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H73" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="I73" t="n">
         <v>157.073893212</v>
       </c>
       <c r="J73" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K73" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L73" t="n">
         <v>19</v>
@@ -8068,7 +8296,7 @@
         <v>0</v>
       </c>
       <c r="S73" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="T73" t="n">
         <v>2</v>
@@ -8085,14 +8313,17 @@
       <c r="X73" t="n">
         <v>3</v>
       </c>
-      <c r="Y73" t="n">
+      <c r="Y73" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z73" t="n">
         <v>156.067120027688</v>
       </c>
-      <c r="Z73"/>
+      <c r="AA73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B74" t="n">
         <v>21.0190217571846</v>
@@ -8104,25 +8335,25 @@
         <v>139783.026062556</v>
       </c>
       <c r="E74" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F74" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="G74" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H74" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="I74" t="n">
         <v>183.089543276</v>
       </c>
       <c r="J74" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K74" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L74" t="n">
         <v>12</v>
@@ -8146,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="S74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
@@ -8161,14 +8392,17 @@
       <c r="X74" t="n">
         <v>2</v>
       </c>
-      <c r="Y74" t="n">
+      <c r="Y74" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z74" t="n">
         <v>182.082017149038</v>
       </c>
-      <c r="Z74"/>
+      <c r="AA74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B75" t="n">
         <v>19.3828091616352</v>
@@ -8180,25 +8414,25 @@
         <v>334110.225654889</v>
       </c>
       <c r="E75" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F75" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G75" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="H75" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="I75" t="n">
         <v>252.085854864</v>
       </c>
       <c r="J75" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K75" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L75" t="n">
         <v>20</v>
@@ -8222,7 +8456,7 @@
         <v>0</v>
       </c>
       <c r="S75" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -8239,14 +8473,17 @@
       <c r="X75" t="n">
         <v>3</v>
       </c>
-      <c r="Y75" t="n">
+      <c r="Y75" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z75" t="n">
         <v>251.077605652771</v>
       </c>
-      <c r="Z75"/>
+      <c r="AA75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B76" t="n">
         <v>29.9340729253498</v>
@@ -8258,25 +8495,25 @@
         <v>297147.410496901</v>
       </c>
       <c r="E76" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F76" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G76" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H76" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="I76" t="n">
         <v>228.074621484</v>
       </c>
       <c r="J76" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K76" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L76" t="n">
         <v>11</v>
@@ -8300,7 +8537,7 @@
         <v>0</v>
       </c>
       <c r="S76" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
@@ -8315,14 +8552,17 @@
       <c r="X76" t="n">
         <v>2</v>
       </c>
-      <c r="Y76" t="n">
+      <c r="Y76" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z76" t="n">
         <v>227.066723576825</v>
       </c>
-      <c r="Z76"/>
+      <c r="AA76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B77" t="n">
         <v>29.0185902225676</v>
@@ -8334,25 +8574,25 @@
         <v>792943.45295576</v>
       </c>
       <c r="E77" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F77" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G77" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H77" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I77" t="n">
         <v>139.02694302</v>
       </c>
       <c r="J77" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K77" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L77" t="n">
         <v>10</v>
@@ -8376,7 +8616,7 @@
         <v>0</v>
       </c>
       <c r="S77" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
@@ -8391,14 +8631,17 @@
       <c r="X77" t="n">
         <v>2</v>
       </c>
-      <c r="Y77" t="n">
+      <c r="Y77" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z77" t="n">
         <v>138.019498321711</v>
       </c>
-      <c r="Z77"/>
+      <c r="AA77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B78" t="n">
         <v>18.2630198078646</v>
@@ -8410,25 +8653,25 @@
         <v>116576.995963443</v>
       </c>
       <c r="E78" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F78" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G78" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="H78" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="I78" t="n">
         <v>126.042927432</v>
       </c>
       <c r="J78" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K78" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L78" t="n">
         <v>16</v>
@@ -8452,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="S78" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
@@ -8469,14 +8712,17 @@
       <c r="X78" t="n">
         <v>3</v>
       </c>
-      <c r="Y78" t="n">
+      <c r="Y78" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z78" t="n">
         <v>125.027137632722</v>
       </c>
-      <c r="Z78"/>
+      <c r="AA78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B79" t="n">
         <v>21.6668098762618</v>
@@ -8488,25 +8734,25 @@
         <v>38699.2431078005</v>
       </c>
       <c r="E79" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F79" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G79" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="H79" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="I79" t="n">
         <v>115.063328528</v>
       </c>
       <c r="J79" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="K79" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L79" t="n">
         <v>7</v>
@@ -8530,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="S79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
@@ -8545,14 +8791,17 @@
       <c r="X79" t="n">
         <v>2</v>
       </c>
-      <c r="Y79"/>
-      <c r="Z79" t="n">
+      <c r="Y79" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z79"/>
+      <c r="AA79" t="n">
         <v>160.04167905468</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B80" t="n">
         <v>21.8955876027618</v>
@@ -8564,25 +8813,25 @@
         <v>17744.1368513998</v>
       </c>
       <c r="E80" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F80" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G80" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="H80" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="I80" t="n">
         <v>173.10519334</v>
       </c>
       <c r="J80" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K80" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L80" t="n">
         <v>5</v>
@@ -8606,7 +8855,7 @@
         <v>0</v>
       </c>
       <c r="S80" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
@@ -8623,12 +8872,15 @@
       <c r="X80" t="n">
         <v>2</v>
       </c>
-      <c r="Y80"/>
+      <c r="Y80" t="s">
+        <v>35</v>
+      </c>
       <c r="Z80"/>
+      <c r="AA80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B81" t="n">
         <v>211.791690421232</v>
@@ -8640,25 +8892,25 @@
         <v>2817470.8187802</v>
       </c>
       <c r="E81" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F81" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="G81" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="H81" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="I81" t="n">
         <v>246.100442308</v>
       </c>
       <c r="J81" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K81" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L81" t="n">
         <v>23</v>
@@ -8682,7 +8934,7 @@
         <v>0</v>
       </c>
       <c r="S81" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="T81" t="n">
         <v>9</v>
@@ -8699,14 +8951,17 @@
       <c r="X81" t="n">
         <v>3</v>
       </c>
-      <c r="Y81" t="n">
+      <c r="Y81" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z81" t="n">
         <v>245.092498458603</v>
       </c>
-      <c r="Z81"/>
+      <c r="AA81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B82" t="n">
         <v>156.427863003705</v>
@@ -8718,25 +8973,25 @@
         <v>2207735.02889453</v>
       </c>
       <c r="E82" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F82" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G82" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H82" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I82" t="n">
         <v>218.105527688</v>
       </c>
       <c r="J82" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K82" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L82" t="n">
         <v>24</v>
@@ -8760,7 +9015,7 @@
         <v>0</v>
       </c>
       <c r="S82" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
@@ -8777,16 +9032,19 @@
       <c r="X82" t="n">
         <v>4</v>
       </c>
-      <c r="Y82" t="n">
+      <c r="Y82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z82" t="n">
         <v>217.097732478695</v>
       </c>
-      <c r="Z82" t="n">
+      <c r="AA82" t="n">
         <v>263.097786731982</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B83" t="n">
         <v>19.1538093084952</v>
@@ -8798,25 +9056,25 @@
         <v>424734.173662312</v>
       </c>
       <c r="E83" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F83" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="G83" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H83" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I83" t="n">
         <v>167.036462148</v>
       </c>
       <c r="J83" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K83" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L83" t="n">
         <v>23</v>
@@ -8840,7 +9098,7 @@
         <v>0</v>
       </c>
       <c r="S83" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T83" t="n">
         <v>1</v>
@@ -8857,14 +9115,17 @@
       <c r="X83" t="n">
         <v>3</v>
       </c>
-      <c r="Y83" t="n">
+      <c r="Y83" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z83" t="n">
         <v>166.029076619263</v>
       </c>
-      <c r="Z83"/>
+      <c r="AA83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B84" t="n">
         <v>20.0820323184802</v>
@@ -8876,25 +9137,25 @@
         <v>2797981.26700202</v>
       </c>
       <c r="E84" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F84" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G84" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H84" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="I84" t="n">
         <v>161.10519334</v>
       </c>
       <c r="J84" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K84" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L84" t="n">
         <v>16</v>
@@ -8918,7 +9179,7 @@
         <v>0</v>
       </c>
       <c r="S84" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T84" t="n">
         <v>1</v>
@@ -8935,14 +9196,17 @@
       <c r="X84" t="n">
         <v>3</v>
       </c>
-      <c r="Y84" t="n">
+      <c r="Y84" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z84" t="n">
         <v>160.053281048355</v>
       </c>
-      <c r="Z84"/>
+      <c r="AA84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B85" t="n">
         <v>121.474549417012</v>
@@ -8954,25 +9218,25 @@
         <v>1392805.15578649</v>
       </c>
       <c r="E85" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F85" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G85" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H85" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="I85" t="n">
         <v>193.037507704</v>
       </c>
       <c r="J85" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K85" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L85" t="n">
         <v>10</v>
@@ -8996,7 +9260,7 @@
         <v>0</v>
       </c>
       <c r="S85" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="T85" t="n">
         <v>2</v>
@@ -9011,14 +9275,17 @@
       <c r="X85" t="n">
         <v>2</v>
       </c>
-      <c r="Y85" t="n">
+      <c r="Y85" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z85" t="n">
         <v>192.030955717092</v>
       </c>
-      <c r="Z85"/>
+      <c r="AA85"/>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B86" t="n">
         <v>140.699205020717</v>
@@ -9030,25 +9297,25 @@
         <v>22926582.4431076</v>
       </c>
       <c r="E86" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="G86" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="H86" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="I86" t="n">
         <v>146.08439832</v>
       </c>
       <c r="J86" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K86" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L86" t="n">
         <v>11</v>
@@ -9072,7 +9339,7 @@
         <v>0</v>
       </c>
       <c r="S86" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
@@ -9089,14 +9356,17 @@
       <c r="X86" t="n">
         <v>3</v>
       </c>
-      <c r="Y86" t="n">
+      <c r="Y86" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z86" t="n">
         <v>145.077798340535</v>
       </c>
-      <c r="Z86"/>
+      <c r="AA86"/>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B87" t="n">
         <v>265.277503206274</v>
@@ -9108,25 +9378,25 @@
         <v>3104074.60086653</v>
       </c>
       <c r="E87" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F87" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G87" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H87" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="I87" t="n">
         <v>362.20932406</v>
       </c>
       <c r="J87" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K87" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L87" t="n">
         <v>44</v>
@@ -9150,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="S87" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="T87" t="n">
         <v>2</v>
@@ -9167,16 +9437,19 @@
       <c r="X87" t="n">
         <v>4</v>
       </c>
-      <c r="Y87" t="n">
+      <c r="Y87" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z87" t="n">
         <v>361.202318252654</v>
       </c>
-      <c r="Z87" t="n">
+      <c r="AA87" t="n">
         <v>407.208456075951</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B88" t="n">
         <v>67.1444816980923</v>
@@ -9188,25 +9461,25 @@
         <v>229539.873366926</v>
       </c>
       <c r="E88" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F88" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G88" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="H88" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="I88" t="n">
         <v>203.105862036</v>
       </c>
       <c r="J88" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K88" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L88" t="n">
         <v>8</v>
@@ -9230,7 +9503,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="T88" t="n">
         <v>3</v>
@@ -9245,14 +9518,17 @@
       <c r="X88" t="n">
         <v>2</v>
       </c>
-      <c r="Y88" t="n">
+      <c r="Y88" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z88" t="n">
         <v>202.097900115583</v>
       </c>
-      <c r="Z88"/>
+      <c r="AA88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B89" t="n">
         <v>18.7023609821865</v>
@@ -9264,25 +9540,25 @@
         <v>154916.185615106</v>
       </c>
       <c r="E89" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F89" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="G89" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="H89" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="I89" t="n">
         <v>221.089937199999</v>
       </c>
       <c r="J89" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K89" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L89" t="n">
         <v>21</v>
@@ -9306,7 +9582,7 @@
         <v>0</v>
       </c>
       <c r="S89" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="T89" t="n">
         <v>1</v>
@@ -9323,16 +9599,19 @@
       <c r="X89" t="n">
         <v>4</v>
       </c>
-      <c r="Y89" t="n">
+      <c r="Y89" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z89" t="n">
         <v>220.075514031239</v>
       </c>
-      <c r="Z89" t="n">
+      <c r="AA89" t="n">
         <v>266.059020393916</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B90" t="n">
         <v>19.6392549193853</v>
@@ -9344,25 +9623,25 @@
         <v>240254.465908962</v>
       </c>
       <c r="E90" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F90" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="G90" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="H90" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="I90" t="n">
         <v>131.058243148</v>
       </c>
       <c r="J90" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K90" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L90" t="n">
         <v>26</v>
@@ -9386,7 +9665,7 @@
         <v>0</v>
       </c>
       <c r="S90" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T90" t="n">
         <v>1</v>
@@ -9403,14 +9682,17 @@
       <c r="X90" t="n">
         <v>3</v>
       </c>
-      <c r="Y90" t="n">
+      <c r="Y90" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z90" t="n">
         <v>130.051732080933</v>
       </c>
-      <c r="Z90"/>
+      <c r="AA90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B91" t="n">
         <v>24.892756971235</v>
@@ -9422,25 +9704,25 @@
         <v>2186254.21117989</v>
       </c>
       <c r="E91" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F91" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="G91" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="H91" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="I91" t="n">
         <v>136.038510748</v>
       </c>
       <c r="J91" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K91" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L91" t="n">
         <v>17</v>
@@ -9464,7 +9746,7 @@
         <v>0</v>
       </c>
       <c r="S91" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
@@ -9481,14 +9763,17 @@
       <c r="X91" t="n">
         <v>3</v>
       </c>
-      <c r="Y91" t="n">
+      <c r="Y91" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z91" t="n">
         <v>135.031626518935</v>
       </c>
-      <c r="Z91"/>
+      <c r="AA91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B92" t="n">
         <v>83.8221244108279</v>
@@ -9500,25 +9785,25 @@
         <v>2463907.29977748</v>
       </c>
       <c r="E92" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F92" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G92" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="H92" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="I92" t="n">
         <v>159.089543276</v>
       </c>
       <c r="J92" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K92" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L92" t="n">
         <v>11</v>
@@ -9542,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="S92" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="T92" t="n">
         <v>5</v>
@@ -9557,14 +9842,17 @@
       <c r="X92" t="n">
         <v>2</v>
       </c>
-      <c r="Y92" t="n">
+      <c r="Y92" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z92" t="n">
         <v>158.083456620975</v>
       </c>
-      <c r="Z92"/>
+      <c r="AA92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B93" t="n">
         <v>20.2714785945618</v>
@@ -9576,25 +9864,25 @@
         <v>275888.154684441</v>
       </c>
       <c r="E93" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F93" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G93" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="H93" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="I93" t="n">
         <v>167.058243148</v>
       </c>
       <c r="J93" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K93" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L93" t="n">
         <v>18</v>
@@ -9618,7 +9906,7 @@
         <v>0</v>
       </c>
       <c r="S93" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T93" t="n">
         <v>1</v>
@@ -9635,14 +9923,17 @@
       <c r="X93" t="n">
         <v>3</v>
       </c>
-      <c r="Y93" t="n">
+      <c r="Y93" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z93" t="n">
         <v>166.052147744218</v>
       </c>
-      <c r="Z93"/>
+      <c r="AA93"/>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B94" t="n">
         <v>42.4609489139566</v>
@@ -9654,25 +9945,25 @@
         <v>4833641.44134822</v>
       </c>
       <c r="E94" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F94" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="G94" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H94" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="I94" t="n">
         <v>205.037507704</v>
       </c>
       <c r="J94" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K94" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L94" t="n">
         <v>23</v>
@@ -9696,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="S94" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="T94" t="n">
         <v>6</v>
@@ -9713,14 +10004,17 @@
       <c r="X94" t="n">
         <v>3</v>
       </c>
-      <c r="Y94" t="n">
+      <c r="Y94" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z94" t="n">
         <v>204.031301725365</v>
       </c>
-      <c r="Z94"/>
+      <c r="AA94"/>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B95" t="n">
         <v>20.8381726841944</v>
@@ -9732,25 +10026,25 @@
         <v>14207.1276275261</v>
       </c>
       <c r="E95" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F95" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="G95" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="H95" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="I95" t="n">
         <v>117.078978592</v>
       </c>
       <c r="J95" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K95" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L95" t="n">
         <v>12</v>
@@ -9774,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="S95" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T95" t="n">
         <v>1</v>
@@ -9789,14 +10083,17 @@
       <c r="X95" t="n">
         <v>2</v>
       </c>
-      <c r="Y95" t="n">
+      <c r="Y95" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z95" t="n">
         <v>116.069951573089</v>
       </c>
-      <c r="Z95"/>
+      <c r="AA95"/>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B96" t="n">
         <v>80.0380438566729</v>
@@ -9808,25 +10105,25 @@
         <v>4025611.52646011</v>
       </c>
       <c r="E96" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F96" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="G96" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="H96" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="I96" t="n">
         <v>340.079432092</v>
       </c>
       <c r="J96" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K96" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L96" t="n">
         <v>20</v>
@@ -9850,7 +10147,7 @@
         <v>0</v>
       </c>
       <c r="S96" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="T96" t="n">
         <v>5</v>
@@ -9867,14 +10164,17 @@
       <c r="X96" t="n">
         <v>3</v>
       </c>
-      <c r="Y96" t="n">
+      <c r="Y96" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z96" t="n">
         <v>339.072658085362</v>
       </c>
-      <c r="Z96"/>
+      <c r="AA96"/>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B97" t="n">
         <v>21.295171231101</v>
@@ -9886,25 +10186,25 @@
         <v>390491.988621884</v>
       </c>
       <c r="E97" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F97" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="G97" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="H97" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="I97" t="n">
         <v>151.04940978</v>
       </c>
       <c r="J97" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K97" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L97" t="n">
         <v>18</v>
@@ -9928,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="S97" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
@@ -9945,16 +10245,19 @@
       <c r="X97" t="n">
         <v>4</v>
       </c>
-      <c r="Y97" t="n">
+      <c r="Y97" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z97" t="n">
         <v>150.039139791229</v>
       </c>
-      <c r="Z97" t="n">
+      <c r="AA97" t="n">
         <v>196.048936978606</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B98" t="n">
         <v>285.816107030399</v>
@@ -9966,25 +10269,25 @@
         <v>859983.683454773</v>
       </c>
       <c r="E98" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F98" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G98" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="H98" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="I98" t="n">
         <v>203.094628656</v>
       </c>
       <c r="J98" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K98" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L98" t="n">
         <v>26</v>
@@ -10008,7 +10311,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="T98" t="n">
         <v>7</v>
@@ -10025,14 +10328,17 @@
       <c r="X98" t="n">
         <v>3</v>
       </c>
-      <c r="Y98" t="n">
+      <c r="Y98" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z98" t="n">
         <v>202.088690437048</v>
       </c>
-      <c r="Z98"/>
+      <c r="AA98"/>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B99" t="n">
         <v>247.189008482992</v>
@@ -10044,25 +10350,25 @@
         <v>90438.0967384805</v>
       </c>
       <c r="E99" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F99" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="G99" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="H99" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="I99" t="n">
         <v>205.0595061</v>
       </c>
       <c r="J99" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K99" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L99" t="n">
         <v>25</v>
@@ -10086,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="S99" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="T99" t="n">
         <v>7</v>
@@ -10103,14 +10409,17 @@
       <c r="X99" t="n">
         <v>3</v>
       </c>
-      <c r="Y99"/>
-      <c r="Z99" t="n">
+      <c r="Y99" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z99"/>
+      <c r="AA99" t="n">
         <v>250.08630414339</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B100" t="n">
         <v>169.601137785765</v>
@@ -10122,25 +10431,25 @@
         <v>823588.99269661</v>
       </c>
       <c r="E100" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F100" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="G100" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="H100" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="I100" t="n">
         <v>193.073893212</v>
       </c>
       <c r="J100" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K100" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L100" t="n">
         <v>24</v>
@@ -10164,7 +10473,7 @@
         <v>0</v>
       </c>
       <c r="S100" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="T100" t="n">
         <v>7</v>
@@ -10181,14 +10490,17 @@
       <c r="X100" t="n">
         <v>3</v>
       </c>
-      <c r="Y100" t="n">
+      <c r="Y100" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z100" t="n">
         <v>192.067888917468</v>
       </c>
-      <c r="Z100"/>
+      <c r="AA100"/>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B101" t="n">
         <v>262.266131952783</v>
@@ -10200,25 +10512,25 @@
         <v>324114.438298485</v>
       </c>
       <c r="E101" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F101" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G101" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="H101" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="I101" t="n">
         <v>238.084123548</v>
       </c>
       <c r="J101" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K101" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="L101" t="n">
         <v>11</v>
@@ -10242,7 +10554,7 @@
         <v>0</v>
       </c>
       <c r="S101" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="T101" t="n">
         <v>7</v>
@@ -10257,14 +10569,17 @@
       <c r="X101" t="n">
         <v>2</v>
       </c>
-      <c r="Y101" t="n">
+      <c r="Y101" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z101" t="n">
         <v>237.077396337791</v>
       </c>
-      <c r="Z101"/>
+      <c r="AA101"/>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B102" t="n">
         <v>27.116783409434</v>
@@ -10276,25 +10591,25 @@
         <v>380309.499879049</v>
       </c>
       <c r="E102" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F102" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G102" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="H102" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="I102" t="n">
         <v>145.073893212</v>
       </c>
       <c r="J102" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K102" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="L102" t="n">
         <v>8</v>
@@ -10318,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="S102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T102" t="n">
         <v>2</v>
@@ -10333,14 +10648,17 @@
       <c r="X102" t="n">
         <v>2</v>
       </c>
-      <c r="Y102" t="n">
+      <c r="Y102" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z102" t="n">
         <v>144.066527051377</v>
       </c>
-      <c r="Z102"/>
+      <c r="AA102"/>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B103" t="n">
         <v>25.517783114454</v>
@@ -10352,25 +10670,25 @@
         <v>471998.578115815</v>
       </c>
       <c r="E103" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F103" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="G103" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="H103" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="I103" t="n">
         <v>183.053157768</v>
       </c>
       <c r="J103" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K103" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="L103" t="n">
         <v>23</v>
@@ -10394,7 +10712,7 @@
         <v>0</v>
       </c>
       <c r="S103" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="T103" t="n">
         <v>1</v>
@@ -10411,16 +10729,19 @@
       <c r="X103" t="n">
         <v>4</v>
       </c>
-      <c r="Y103" t="n">
+      <c r="Y103" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z103" t="n">
         <v>182.045426046238</v>
       </c>
-      <c r="Z103" t="n">
+      <c r="AA103" t="n">
         <v>228.016310464981</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B104" t="n">
         <v>22.539227355674</v>
@@ -10432,25 +10753,25 @@
         <v>1820776.3275138</v>
       </c>
       <c r="E104" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="F104" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="G104" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="H104" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I104" t="n">
         <v>149.070145224</v>
       </c>
       <c r="J104" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K104" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="L104" t="n">
         <v>5</v>
@@ -10474,7 +10795,7 @@
         <v>0</v>
       </c>
       <c r="S104" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T104" t="n">
         <v>1</v>
@@ -10489,14 +10810,17 @@
       <c r="X104" t="n">
         <v>2</v>
       </c>
-      <c r="Y104" t="n">
+      <c r="Y104" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z104" t="n">
         <v>148.062668472646</v>
       </c>
-      <c r="Z104"/>
+      <c r="AA104"/>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B105" t="n">
         <v>148.34670324655</v>
@@ -10508,25 +10832,25 @@
         <v>21006.4638474871</v>
       </c>
       <c r="E105" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="F105" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="G105" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="H105" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="I105" t="n">
         <v>114.06807956</v>
       </c>
       <c r="J105" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K105" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="L105" t="n">
         <v>8</v>
@@ -10550,7 +10874,7 @@
         <v>0</v>
       </c>
       <c r="S105" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="T105" t="n">
         <v>2</v>
@@ -10565,12 +10889,15 @@
       <c r="X105" t="n">
         <v>1</v>
       </c>
-      <c r="Y105"/>
+      <c r="Y105" t="s">
+        <v>35</v>
+      </c>
       <c r="Z105"/>
+      <c r="AA105"/>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B106" t="n">
         <v>230.652363215669</v>
@@ -10582,25 +10909,25 @@
         <v>2801584.00935964</v>
       </c>
       <c r="E106" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F106" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="G106" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="H106" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="I106" t="n">
         <v>232.121177752</v>
       </c>
       <c r="J106" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K106" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="L106" t="n">
         <v>32</v>
@@ -10624,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="S106" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="T106" t="n">
         <v>7</v>
@@ -10641,14 +10968,17 @@
       <c r="X106" t="n">
         <v>3</v>
       </c>
-      <c r="Y106" t="n">
+      <c r="Y106" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z106" t="n">
         <v>231.113936166736</v>
       </c>
-      <c r="Z106"/>
+      <c r="AA106"/>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B107" t="n">
         <v>30.6492495856024</v>
@@ -10660,25 +10990,25 @@
         <v>4267727.2981444</v>
       </c>
       <c r="E107" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="F107" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="G107" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H107" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="I107" t="n">
         <v>217.131408088</v>
       </c>
       <c r="J107" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K107" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="L107" t="n">
         <v>8</v>
@@ -10702,7 +11032,7 @@
         <v>0</v>
       </c>
       <c r="S107" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T107" t="n">
         <v>2</v>
@@ -10719,12 +11049,15 @@
       <c r="X107" t="n">
         <v>2</v>
       </c>
-      <c r="Y107"/>
+      <c r="Y107" t="s">
+        <v>35</v>
+      </c>
       <c r="Z107"/>
+      <c r="AA107"/>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B108" t="n">
         <v>21.4954459328415</v>
@@ -10736,25 +11069,25 @@
         <v>402802.979517452</v>
       </c>
       <c r="E108" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="F108" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="G108" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="H108" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="I108" t="n">
         <v>227.090605896</v>
       </c>
       <c r="J108" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K108" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="L108" t="n">
         <v>26</v>
@@ -10778,7 +11111,7 @@
         <v>0</v>
       </c>
       <c r="S108" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="T108" t="n">
         <v>1</v>
@@ -10795,16 +11128,19 @@
       <c r="X108" t="n">
         <v>4</v>
       </c>
-      <c r="Y108" t="n">
+      <c r="Y108" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z108" t="n">
         <v>226.083904391548</v>
       </c>
-      <c r="Z108" t="n">
+      <c r="AA108" t="n">
         <v>272.080907791577</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B109" t="n">
         <v>210.953414731294</v>
@@ -10816,25 +11152,25 @@
         <v>16271.1193489505</v>
       </c>
       <c r="E109" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="F109" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="G109" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="H109" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="I109" t="n">
         <v>118.062994179999</v>
       </c>
       <c r="J109" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K109" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="L109" t="n">
         <v>6</v>
@@ -10858,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="S109" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="T109" t="n">
         <v>7</v>
@@ -10873,14 +11209,17 @@
       <c r="X109" t="n">
         <v>2</v>
       </c>
-      <c r="Y109" t="n">
+      <c r="Y109" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z109" t="n">
         <v>117.055682421239</v>
       </c>
-      <c r="Z109"/>
+      <c r="AA109"/>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B110" t="n">
         <v>169.541804119959</v>
@@ -10892,25 +11231,25 @@
         <v>5744180.67212621</v>
       </c>
       <c r="E110" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="F110" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="G110" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="H110" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="I110" t="n">
         <v>432.867189147999</v>
       </c>
       <c r="J110" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K110" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="L110" t="n">
         <v>26</v>
@@ -10934,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="S110" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="T110" t="n">
         <v>1</v>
@@ -10951,14 +11290,17 @@
       <c r="X110" t="n">
         <v>3</v>
       </c>
-      <c r="Y110" t="n">
+      <c r="Y110" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z110" t="n">
         <v>431.862613877381</v>
       </c>
-      <c r="Z110"/>
+      <c r="AA110"/>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B111" t="n">
         <v>243.046564789378</v>
@@ -10970,25 +11312,25 @@
         <v>9015547.99954974</v>
       </c>
       <c r="E111" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F111" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="G111" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="H111" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="I111" t="n">
         <v>524.893403896</v>
       </c>
       <c r="J111" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K111" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="L111" t="n">
         <v>16</v>
@@ -11012,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="S111" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="T111" t="n">
         <v>4</v>
@@ -11027,14 +11369,17 @@
       <c r="X111" t="n">
         <v>2</v>
       </c>
-      <c r="Y111" t="n">
+      <c r="Y111" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z111" t="n">
         <v>523.884330705689</v>
       </c>
-      <c r="Z111"/>
+      <c r="AA111"/>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B112" t="n">
         <v>19.4344454665015</v>
@@ -11046,25 +11391,25 @@
         <v>1485774.09023052</v>
       </c>
       <c r="E112" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="F112" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="G112" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="H112" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="I112" t="n">
         <v>111.04326178</v>
       </c>
       <c r="J112" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K112" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="L112" t="n">
         <v>15</v>
@@ -11088,7 +11433,7 @@
         <v>0</v>
       </c>
       <c r="S112" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T112" t="n">
         <v>1</v>
@@ -11105,12 +11450,15 @@
       <c r="X112" t="n">
         <v>2</v>
       </c>
-      <c r="Y112"/>
+      <c r="Y112" t="s">
+        <v>35</v>
+      </c>
       <c r="Z112"/>
+      <c r="AA112"/>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B113" t="n">
         <v>30.6145237275529</v>
@@ -11122,25 +11470,25 @@
         <v>19406.6916079564</v>
       </c>
       <c r="E113" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="F113" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="G113" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="H113" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="I113" t="n">
         <v>131.094628656</v>
       </c>
       <c r="J113" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K113" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="L113" t="n">
         <v>6</v>
@@ -11164,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="S113" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T113" t="n">
         <v>1</v>
@@ -11179,14 +11527,17 @@
       <c r="X113" t="n">
         <v>2</v>
       </c>
-      <c r="Y113" t="n">
+      <c r="Y113" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z113" t="n">
         <v>130.088022486844</v>
       </c>
-      <c r="Z113"/>
+      <c r="AA113"/>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B114" t="n">
         <v>92.2931598572243</v>
@@ -11198,25 +11549,25 @@
         <v>1962390.64578434</v>
       </c>
       <c r="E114" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="F114" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="G114" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H114" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="I114" t="n">
         <v>191.061614276</v>
       </c>
       <c r="J114" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K114" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="L114" t="n">
         <v>19</v>
@@ -11240,7 +11591,7 @@
         <v>1</v>
       </c>
       <c r="S114" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="T114" t="n">
         <v>4</v>
@@ -11257,14 +11608,17 @@
       <c r="X114" t="n">
         <v>3</v>
       </c>
-      <c r="Y114" t="n">
+      <c r="Y114" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z114" t="n">
         <v>190.054429959185</v>
       </c>
-      <c r="Z114"/>
+      <c r="AA114"/>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B115" t="n">
         <v>173.401270305867</v>
@@ -11276,25 +11630,25 @@
         <v>17479764.4023572</v>
       </c>
       <c r="E115" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="F115" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="G115" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="H115" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="I115" t="n">
         <v>219.125928784</v>
       </c>
       <c r="J115" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K115" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="L115" t="n">
         <v>23</v>
@@ -11318,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="S115" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="T115" t="n">
         <v>4</v>
@@ -11335,14 +11689,17 @@
       <c r="X115" t="n">
         <v>3</v>
       </c>
-      <c r="Y115" t="n">
+      <c r="Y115" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z115" t="n">
         <v>218.118363432602</v>
       </c>
-      <c r="Z115"/>
+      <c r="AA115"/>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B116" t="n">
         <v>18.7324711917051</v>
@@ -11354,25 +11711,25 @@
         <v>238393.589883474</v>
       </c>
       <c r="E116" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="F116" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="G116" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="H116" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="I116" t="n">
         <v>125.014664083999</v>
       </c>
       <c r="J116" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K116" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="L116" t="n">
         <v>22</v>
@@ -11396,7 +11753,7 @@
         <v>0</v>
       </c>
       <c r="S116" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T116" t="n">
         <v>1</v>
@@ -11413,14 +11770,17 @@
       <c r="X116" t="n">
         <v>3</v>
       </c>
-      <c r="Y116" t="n">
+      <c r="Y116" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z116" t="n">
         <v>124.007316123599</v>
       </c>
-      <c r="Z116"/>
+      <c r="AA116"/>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B117" t="n">
         <v>366.425027171272</v>
@@ -11432,25 +11792,25 @@
         <v>980930.587431473</v>
       </c>
       <c r="E117" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="F117" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="G117" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="H117" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="I117" t="n">
         <v>411.184586531999</v>
       </c>
       <c r="J117" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K117" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="L117" t="n">
         <v>27</v>
@@ -11474,7 +11834,7 @@
         <v>0</v>
       </c>
       <c r="S117" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="T117" t="n">
         <v>5</v>
@@ -11491,14 +11851,17 @@
       <c r="X117" t="n">
         <v>3</v>
       </c>
-      <c r="Y117" t="n">
+      <c r="Y117" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z117" t="n">
         <v>410.17544195571</v>
       </c>
-      <c r="Z117"/>
+      <c r="AA117"/>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B118" t="n">
         <v>300.798773041369</v>
@@ -11510,25 +11873,25 @@
         <v>6726485.29974905</v>
       </c>
       <c r="E118" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="F118" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="G118" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="H118" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="I118" t="n">
         <v>776.686699831999</v>
       </c>
       <c r="J118" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K118" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="L118" t="n">
         <v>13</v>
@@ -11552,7 +11915,7 @@
         <v>0</v>
       </c>
       <c r="S118" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="T118" t="n">
         <v>1</v>
@@ -11567,14 +11930,17 @@
       <c r="X118" t="n">
         <v>2</v>
       </c>
-      <c r="Y118" t="n">
+      <c r="Y118" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z118" t="n">
         <v>775.680757277326</v>
       </c>
-      <c r="Z118"/>
+      <c r="AA118"/>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B119" t="n">
         <v>309.005184142657</v>
@@ -11586,25 +11952,25 @@
         <v>2012127.88342095</v>
       </c>
       <c r="E119" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="F119" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="G119" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="H119" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="I119" t="n">
         <v>499.296759159999</v>
       </c>
       <c r="J119" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K119" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="L119" t="n">
         <v>28</v>
@@ -11628,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="S119" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="T119" t="n">
         <v>4</v>
@@ -11645,14 +12011,17 @@
       <c r="X119" t="n">
         <v>3</v>
       </c>
-      <c r="Y119" t="n">
+      <c r="Y119" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z119" t="n">
         <v>498.287888708547</v>
       </c>
-      <c r="Z119"/>
+      <c r="AA119"/>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B120" t="n">
         <v>546.918786116408</v>
@@ -11664,25 +12033,25 @@
         <v>748666.438162909</v>
       </c>
       <c r="E120" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="F120" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="G120" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="H120" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="I120" t="n">
         <v>284.214015516</v>
       </c>
       <c r="J120" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K120" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="L120" t="n">
         <v>22</v>
@@ -11706,7 +12075,7 @@
         <v>0</v>
       </c>
       <c r="S120" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="T120" t="n">
         <v>10</v>
@@ -11723,12 +12092,15 @@
       <c r="X120" t="n">
         <v>2</v>
       </c>
-      <c r="Y120"/>
+      <c r="Y120" t="s">
+        <v>35</v>
+      </c>
       <c r="Z120"/>
+      <c r="AA120"/>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B121" t="n">
         <v>335.25144720316</v>
@@ -11740,25 +12112,25 @@
         <v>1527489.66962334</v>
       </c>
       <c r="E121" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="F121" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="G121" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="H121" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="I121" t="n">
         <v>408.28757438</v>
       </c>
       <c r="J121" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K121" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="L121" t="n">
         <v>23</v>
@@ -11782,7 +12154,7 @@
         <v>0</v>
       </c>
       <c r="S121" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="T121" t="n">
         <v>3</v>
@@ -11797,16 +12169,19 @@
       <c r="X121" t="n">
         <v>3</v>
       </c>
-      <c r="Y121" t="n">
+      <c r="Y121" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z121" t="n">
         <v>407.281312066726</v>
       </c>
-      <c r="Z121" t="n">
+      <c r="AA121" t="n">
         <v>453.282664623678</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B122" t="n">
         <v>395.244516009282</v>
@@ -11818,25 +12193,25 @@
         <v>3344997.11918815</v>
       </c>
       <c r="E122" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="F122" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="G122" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="H122" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="I122" t="n">
         <v>286.21440944</v>
       </c>
       <c r="J122" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K122" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="L122" t="n">
         <v>11</v>
@@ -11860,7 +12235,7 @@
         <v>0</v>
       </c>
       <c r="S122" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="T122" t="n">
         <v>4</v>
@@ -11875,14 +12250,17 @@
       <c r="X122" t="n">
         <v>2</v>
       </c>
-      <c r="Y122" t="n">
+      <c r="Y122" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z122" t="n">
         <v>285.207032172515</v>
       </c>
-      <c r="Z122"/>
+      <c r="AA122"/>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B123" t="n">
         <v>345.610554843817</v>
@@ -11894,25 +12272,25 @@
         <v>91387.9430611044</v>
       </c>
       <c r="E123" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="F123" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G123" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="H123" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="I123" t="n">
         <v>392.29265976</v>
       </c>
       <c r="J123" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K123" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="L123" t="n">
         <v>6</v>
@@ -11936,7 +12314,7 @@
         <v>0</v>
       </c>
       <c r="S123" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="T123" t="n">
         <v>4</v>
@@ -11949,16 +12327,19 @@
       <c r="X123" t="n">
         <v>2</v>
       </c>
-      <c r="Y123" t="n">
+      <c r="Y123" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z123" t="n">
         <v>391.282107453128</v>
       </c>
-      <c r="Z123" t="n">
+      <c r="AA123" t="n">
         <v>437.283075353609</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B124" t="n">
         <v>280.814492930482</v>
@@ -11970,25 +12351,25 @@
         <v>2569176.15779386</v>
       </c>
       <c r="E124" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="F124" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="G124" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="H124" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="I124" t="n">
         <v>515.29167378</v>
       </c>
       <c r="J124" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K124" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="L124" t="n">
         <v>34</v>
@@ -12012,7 +12393,7 @@
         <v>0</v>
       </c>
       <c r="S124" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="T124" t="n">
         <v>5</v>
@@ -12029,14 +12410,17 @@
       <c r="X124" t="n">
         <v>3</v>
       </c>
-      <c r="Y124" t="n">
+      <c r="Y124" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z124" t="n">
         <v>514.28319734487</v>
       </c>
-      <c r="Z124"/>
+      <c r="AA124"/>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B125" t="n">
         <v>311.512606498645</v>
@@ -12048,25 +12432,25 @@
         <v>54768.460502726</v>
       </c>
       <c r="E125" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="F125" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="G125" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="H125" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="I125" t="n">
         <v>499.296759159999</v>
       </c>
       <c r="J125" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K125" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="L125" t="n">
         <v>17</v>
@@ -12090,7 +12474,7 @@
         <v>0</v>
       </c>
       <c r="S125" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="T125" t="n">
         <v>5</v>
@@ -12105,14 +12489,17 @@
       <c r="X125" t="n">
         <v>2</v>
       </c>
-      <c r="Y125" t="n">
+      <c r="Y125" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z125" t="n">
         <v>498.287719196602</v>
       </c>
-      <c r="Z125"/>
+      <c r="AA125"/>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B126" t="n">
         <v>398.33039004463</v>
@@ -12124,25 +12511,25 @@
         <v>5713.77824559262</v>
       </c>
       <c r="E126" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="F126" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="G126" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="H126" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="I126" t="n">
         <v>178.099379688</v>
       </c>
       <c r="J126" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K126" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L126" t="n">
         <v>12</v>
@@ -12166,7 +12553,7 @@
         <v>0</v>
       </c>
       <c r="S126" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="T126" t="n">
         <v>7</v>
@@ -12183,12 +12570,15 @@
       <c r="X126" t="n">
         <v>2</v>
       </c>
-      <c r="Y126"/>
+      <c r="Y126" t="s">
+        <v>35</v>
+      </c>
       <c r="Z126"/>
+      <c r="AA126"/>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B127" t="n">
         <v>396.04367728604</v>
@@ -12200,25 +12590,25 @@
         <v>963756.616399379</v>
       </c>
       <c r="E127" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="F127" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="G127" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="H127" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I127" t="n">
         <v>230.151809184</v>
       </c>
       <c r="J127" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K127" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L127" t="n">
         <v>11</v>
@@ -12242,7 +12632,7 @@
         <v>0</v>
       </c>
       <c r="S127" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="T127" t="n">
         <v>7</v>
@@ -12257,14 +12647,17 @@
       <c r="X127" t="n">
         <v>2</v>
       </c>
-      <c r="Y127" t="n">
+      <c r="Y127" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z127" t="n">
         <v>229.162705174953</v>
       </c>
-      <c r="Z127"/>
+      <c r="AA127"/>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B128" t="n">
         <v>389.184592051184</v>
@@ -12276,25 +12669,25 @@
         <v>8966.72285531691</v>
       </c>
       <c r="E128" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="F128" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="G128" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="H128" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="I128" t="n">
         <v>186.161979944</v>
       </c>
       <c r="J128" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K128" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L128" t="n">
         <v>4</v>
@@ -12318,7 +12711,7 @@
         <v>0</v>
       </c>
       <c r="S128" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="T128" t="n">
         <v>5</v>
@@ -12333,8 +12726,11 @@
       <c r="X128" t="n">
         <v>1</v>
       </c>
-      <c r="Y128"/>
+      <c r="Y128" t="s">
+        <v>35</v>
+      </c>
       <c r="Z128"/>
+      <c r="AA128"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
